--- a/output/upload/S00022_1833_Wealth직장인연금보험_무배당.xlsx
+++ b/output/upload/S00022_1833_Wealth직장인연금보험_무배당.xlsx
@@ -1372,17 +1372,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>1833026</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>1833026</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">

--- a/output/upload/S00022_1833_Wealth직장인연금보험_무배당.xlsx
+++ b/output/upload/S00022_1833_Wealth직장인연금보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD32"/>
+  <dimension ref="A1:AD42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -1416,13 +1416,21 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I8" s="6" t="n"/>
       <c r="J8" s="6" t="n"/>
       <c r="K8" s="6" t="n"/>
@@ -1432,7 +1440,11 @@
       <c r="O8" s="6" t="n"/>
       <c r="P8" s="6" t="n"/>
       <c r="Q8" s="6" t="n"/>
-      <c r="R8" s="6" t="n"/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S8" s="6" t="n"/>
       <c r="T8" s="6" t="n"/>
       <c r="U8" s="6" t="n"/>
@@ -1448,13 +1460,21 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="6" t="n"/>
@@ -1464,7 +1484,11 @@
       <c r="O9" s="6" t="n"/>
       <c r="P9" s="6" t="n"/>
       <c r="Q9" s="6" t="n"/>
-      <c r="R9" s="6" t="n"/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S9" s="6" t="n"/>
       <c r="T9" s="6" t="n"/>
       <c r="U9" s="6" t="n"/>
@@ -1480,13 +1504,21 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I10" s="6" t="n"/>
       <c r="J10" s="6" t="n"/>
       <c r="K10" s="6" t="n"/>
@@ -1496,7 +1528,11 @@
       <c r="O10" s="6" t="n"/>
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
-      <c r="R10" s="6" t="n"/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S10" s="6" t="n"/>
       <c r="T10" s="6" t="n"/>
       <c r="U10" s="6" t="n"/>
@@ -1512,13 +1548,21 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="6" t="n"/>
@@ -1528,7 +1572,11 @@
       <c r="O11" s="6" t="n"/>
       <c r="P11" s="6" t="n"/>
       <c r="Q11" s="6" t="n"/>
-      <c r="R11" s="6" t="n"/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="6" t="n"/>
       <c r="U11" s="6" t="n"/>
@@ -1544,13 +1592,21 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="6" t="n"/>
       <c r="K12" s="6" t="n"/>
@@ -1560,7 +1616,11 @@
       <c r="O12" s="6" t="n"/>
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="6" t="n"/>
-      <c r="R12" s="6" t="n"/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
@@ -1576,13 +1636,21 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
@@ -1592,7 +1660,11 @@
       <c r="O13" s="6" t="n"/>
       <c r="P13" s="6" t="n"/>
       <c r="Q13" s="6" t="n"/>
-      <c r="R13" s="6" t="n"/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
@@ -1608,13 +1680,21 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="6" t="n"/>
       <c r="K14" s="6" t="n"/>
@@ -1624,7 +1704,11 @@
       <c r="O14" s="6" t="n"/>
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="6" t="n"/>
-      <c r="R14" s="6" t="n"/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
@@ -1640,13 +1724,21 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="6" t="n"/>
@@ -1656,7 +1748,11 @@
       <c r="O15" s="6" t="n"/>
       <c r="P15" s="6" t="n"/>
       <c r="Q15" s="6" t="n"/>
-      <c r="R15" s="6" t="n"/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
@@ -1672,13 +1768,21 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
+      <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="n"/>
       <c r="K16" s="6" t="n"/>
@@ -1688,7 +1792,11 @@
       <c r="O16" s="6" t="n"/>
       <c r="P16" s="6" t="n"/>
       <c r="Q16" s="6" t="n"/>
-      <c r="R16" s="6" t="n"/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
@@ -1704,13 +1812,21 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
@@ -1720,7 +1836,11 @@
       <c r="O17" s="6" t="n"/>
       <c r="P17" s="6" t="n"/>
       <c r="Q17" s="6" t="n"/>
-      <c r="R17" s="6" t="n"/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
@@ -1736,13 +1856,21 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
+      <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="n"/>
       <c r="K18" s="6" t="n"/>
@@ -1752,7 +1880,11 @@
       <c r="O18" s="6" t="n"/>
       <c r="P18" s="6" t="n"/>
       <c r="Q18" s="6" t="n"/>
-      <c r="R18" s="6" t="n"/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
@@ -1768,13 +1900,21 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="6" t="n"/>
@@ -1784,7 +1924,11 @@
       <c r="O19" s="6" t="n"/>
       <c r="P19" s="6" t="n"/>
       <c r="Q19" s="6" t="n"/>
-      <c r="R19" s="6" t="n"/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="6" t="n"/>
       <c r="U19" s="6" t="n"/>
@@ -1800,13 +1944,21 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
+      <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I20" s="6" t="n"/>
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="6" t="n"/>
@@ -1816,7 +1968,11 @@
       <c r="O20" s="6" t="n"/>
       <c r="P20" s="6" t="n"/>
       <c r="Q20" s="6" t="n"/>
-      <c r="R20" s="6" t="n"/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
       <c r="U20" s="6" t="n"/>
@@ -1832,13 +1988,21 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
@@ -1848,7 +2012,11 @@
       <c r="O21" s="6" t="n"/>
       <c r="P21" s="6" t="n"/>
       <c r="Q21" s="6" t="n"/>
-      <c r="R21" s="6" t="n"/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
       <c r="U21" s="6" t="n"/>
@@ -1864,13 +2032,21 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
+      <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="n"/>
@@ -1880,7 +2056,11 @@
       <c r="O22" s="6" t="n"/>
       <c r="P22" s="6" t="n"/>
       <c r="Q22" s="6" t="n"/>
-      <c r="R22" s="6" t="n"/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="6" t="n"/>
       <c r="U22" s="6" t="n"/>
@@ -1896,13 +2076,21 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
+      <c r="B23" s="5" t="inlineStr"/>
       <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
+      <c r="D23" s="5" t="inlineStr"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -1912,7 +2100,11 @@
       <c r="O23" s="6" t="n"/>
       <c r="P23" s="6" t="n"/>
       <c r="Q23" s="6" t="n"/>
-      <c r="R23" s="6" t="n"/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S23" s="6" t="n"/>
       <c r="T23" s="6" t="n"/>
       <c r="U23" s="6" t="n"/>
@@ -1928,13 +2120,21 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="n"/>
+      <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
+      <c r="D24" s="5" t="inlineStr"/>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I24" s="6" t="n"/>
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="n"/>
@@ -1944,7 +2144,11 @@
       <c r="O24" s="6" t="n"/>
       <c r="P24" s="6" t="n"/>
       <c r="Q24" s="6" t="n"/>
-      <c r="R24" s="6" t="n"/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S24" s="6" t="n"/>
       <c r="T24" s="6" t="n"/>
       <c r="U24" s="6" t="n"/>
@@ -1960,13 +2164,21 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="n"/>
+      <c r="B25" s="5" t="inlineStr"/>
       <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
+      <c r="D25" s="5" t="inlineStr"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="n"/>
@@ -1976,7 +2188,11 @@
       <c r="O25" s="6" t="n"/>
       <c r="P25" s="6" t="n"/>
       <c r="Q25" s="6" t="n"/>
-      <c r="R25" s="6" t="n"/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S25" s="6" t="n"/>
       <c r="T25" s="6" t="n"/>
       <c r="U25" s="6" t="n"/>
@@ -1992,13 +2208,21 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="n"/>
+      <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
+      <c r="D26" s="5" t="inlineStr"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="n"/>
@@ -2008,7 +2232,11 @@
       <c r="O26" s="6" t="n"/>
       <c r="P26" s="6" t="n"/>
       <c r="Q26" s="6" t="n"/>
-      <c r="R26" s="6" t="n"/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S26" s="6" t="n"/>
       <c r="T26" s="6" t="n"/>
       <c r="U26" s="6" t="n"/>
@@ -2024,13 +2252,21 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="n"/>
+      <c r="B27" s="5" t="inlineStr"/>
       <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
+      <c r="D27" s="5" t="inlineStr"/>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n"/>
@@ -2040,7 +2276,11 @@
       <c r="O27" s="6" t="n"/>
       <c r="P27" s="6" t="n"/>
       <c r="Q27" s="6" t="n"/>
-      <c r="R27" s="6" t="n"/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S27" s="6" t="n"/>
       <c r="T27" s="6" t="n"/>
       <c r="U27" s="6" t="n"/>
@@ -2056,13 +2296,21 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="n"/>
+      <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
+      <c r="D28" s="5" t="inlineStr"/>
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="6" t="n"/>
@@ -2072,7 +2320,11 @@
       <c r="O28" s="6" t="n"/>
       <c r="P28" s="6" t="n"/>
       <c r="Q28" s="6" t="n"/>
-      <c r="R28" s="6" t="n"/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S28" s="6" t="n"/>
       <c r="T28" s="6" t="n"/>
       <c r="U28" s="6" t="n"/>
@@ -2088,13 +2340,21 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="n"/>
+      <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
+      <c r="D29" s="5" t="inlineStr"/>
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="6" t="n"/>
@@ -2104,7 +2364,11 @@
       <c r="O29" s="6" t="n"/>
       <c r="P29" s="6" t="n"/>
       <c r="Q29" s="6" t="n"/>
-      <c r="R29" s="6" t="n"/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S29" s="6" t="n"/>
       <c r="T29" s="6" t="n"/>
       <c r="U29" s="6" t="n"/>
@@ -2120,13 +2384,21 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="n"/>
+      <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
+      <c r="D30" s="5" t="inlineStr"/>
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="6" t="n"/>
@@ -2136,7 +2408,11 @@
       <c r="O30" s="6" t="n"/>
       <c r="P30" s="6" t="n"/>
       <c r="Q30" s="6" t="n"/>
-      <c r="R30" s="6" t="n"/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S30" s="6" t="n"/>
       <c r="T30" s="6" t="n"/>
       <c r="U30" s="6" t="n"/>
@@ -2152,13 +2428,21 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="n"/>
+      <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
+      <c r="D31" s="5" t="inlineStr"/>
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n"/>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="6" t="n"/>
@@ -2168,7 +2452,11 @@
       <c r="O31" s="6" t="n"/>
       <c r="P31" s="6" t="n"/>
       <c r="Q31" s="6" t="n"/>
-      <c r="R31" s="6" t="n"/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S31" s="6" t="n"/>
       <c r="T31" s="6" t="n"/>
       <c r="U31" s="6" t="n"/>
@@ -2184,13 +2472,21 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="n"/>
+      <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
+      <c r="D32" s="5" t="inlineStr"/>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="5" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="n"/>
@@ -2200,7 +2496,11 @@
       <c r="O32" s="6" t="n"/>
       <c r="P32" s="6" t="n"/>
       <c r="Q32" s="6" t="n"/>
-      <c r="R32" s="6" t="n"/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="S32" s="6" t="n"/>
       <c r="T32" s="6" t="n"/>
       <c r="U32" s="6" t="n"/>
@@ -2214,6 +2514,196 @@
       <c r="AC32" s="6" t="n"/>
       <c r="AD32" s="6" t="n"/>
     </row>
+    <row r="33">
+      <c r="B33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="R3:AD3"/>

--- a/output/upload/S00022_1833_Wealth직장인연금보험_무배당.xlsx
+++ b/output/upload/S00022_1833_Wealth직장인연금보험_무배당.xlsx
@@ -1372,11 +1372,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -1416,11 +1436,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -1460,11 +1500,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -1504,11 +1564,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -1548,11 +1628,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -1592,11 +1692,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -1636,11 +1756,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -1680,11 +1820,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -1724,11 +1884,31 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -1768,11 +1948,31 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -1812,11 +2012,31 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -1856,11 +2076,31 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -1900,11 +2140,31 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -1944,11 +2204,31 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -1988,11 +2268,31 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2032,11 +2332,31 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2076,11 +2396,31 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2120,11 +2460,31 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2164,11 +2524,31 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="inlineStr"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2208,11 +2588,31 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="inlineStr"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2252,11 +2652,31 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="inlineStr"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2296,11 +2716,31 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2340,11 +2780,31 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="inlineStr"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2384,11 +2844,31 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2428,11 +2908,31 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="inlineStr"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2472,11 +2972,31 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="inlineStr"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2515,8 +3035,31 @@
       <c r="AD32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2534,8 +3077,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2553,8 +3119,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2572,8 +3161,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2591,8 +3203,31 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2610,8 +3245,31 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2629,8 +3287,31 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2648,8 +3329,31 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2667,8 +3371,31 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -2686,8 +3413,31 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00022</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260130</t>

--- a/output/upload/S00022_1833_Wealth직장인연금보험_무배당.xlsx
+++ b/output/upload/S00022_1833_Wealth직장인연금보험_무배당.xlsx
@@ -1384,7 +1384,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">

--- a/output/upload/S00022_1833_Wealth직장인연금보험_무배당.xlsx
+++ b/output/upload/S00022_1833_Wealth직장인연금보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD42"/>
+  <dimension ref="A1:AD32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -1438,22 +1438,22 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1500,41 +1500,13 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="6" t="n"/>
@@ -1544,11 +1516,7 @@
       <c r="O9" s="6" t="n"/>
       <c r="P9" s="6" t="n"/>
       <c r="Q9" s="6" t="n"/>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R9" s="6" t="n"/>
       <c r="S9" s="6" t="n"/>
       <c r="T9" s="6" t="n"/>
       <c r="U9" s="6" t="n"/>
@@ -1564,41 +1532,13 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
       <c r="I10" s="6" t="n"/>
       <c r="J10" s="6" t="n"/>
       <c r="K10" s="6" t="n"/>
@@ -1608,11 +1548,7 @@
       <c r="O10" s="6" t="n"/>
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R10" s="6" t="n"/>
       <c r="S10" s="6" t="n"/>
       <c r="T10" s="6" t="n"/>
       <c r="U10" s="6" t="n"/>
@@ -1628,41 +1564,13 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="6" t="n"/>
@@ -1672,11 +1580,7 @@
       <c r="O11" s="6" t="n"/>
       <c r="P11" s="6" t="n"/>
       <c r="Q11" s="6" t="n"/>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R11" s="6" t="n"/>
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="6" t="n"/>
       <c r="U11" s="6" t="n"/>
@@ -1692,41 +1596,13 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="6" t="n"/>
       <c r="K12" s="6" t="n"/>
@@ -1736,11 +1612,7 @@
       <c r="O12" s="6" t="n"/>
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="6" t="n"/>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R12" s="6" t="n"/>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
@@ -1756,41 +1628,13 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
@@ -1800,11 +1644,7 @@
       <c r="O13" s="6" t="n"/>
       <c r="P13" s="6" t="n"/>
       <c r="Q13" s="6" t="n"/>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
@@ -1820,41 +1660,13 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="6" t="n"/>
       <c r="K14" s="6" t="n"/>
@@ -1864,11 +1676,7 @@
       <c r="O14" s="6" t="n"/>
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="6" t="n"/>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R14" s="6" t="n"/>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
@@ -1884,41 +1692,13 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="6" t="n"/>
@@ -1928,11 +1708,7 @@
       <c r="O15" s="6" t="n"/>
       <c r="P15" s="6" t="n"/>
       <c r="Q15" s="6" t="n"/>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R15" s="6" t="n"/>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
@@ -1948,41 +1724,13 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="n"/>
       <c r="K16" s="6" t="n"/>
@@ -1992,11 +1740,7 @@
       <c r="O16" s="6" t="n"/>
       <c r="P16" s="6" t="n"/>
       <c r="Q16" s="6" t="n"/>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
@@ -2012,41 +1756,13 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
@@ -2056,11 +1772,7 @@
       <c r="O17" s="6" t="n"/>
       <c r="P17" s="6" t="n"/>
       <c r="Q17" s="6" t="n"/>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
@@ -2076,41 +1788,13 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="n"/>
       <c r="K18" s="6" t="n"/>
@@ -2120,11 +1804,7 @@
       <c r="O18" s="6" t="n"/>
       <c r="P18" s="6" t="n"/>
       <c r="Q18" s="6" t="n"/>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R18" s="6" t="n"/>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
@@ -2140,41 +1820,13 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="6" t="n"/>
@@ -2184,11 +1836,7 @@
       <c r="O19" s="6" t="n"/>
       <c r="P19" s="6" t="n"/>
       <c r="Q19" s="6" t="n"/>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R19" s="6" t="n"/>
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="6" t="n"/>
       <c r="U19" s="6" t="n"/>
@@ -2204,41 +1852,13 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
       <c r="I20" s="6" t="n"/>
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="6" t="n"/>
@@ -2248,11 +1868,7 @@
       <c r="O20" s="6" t="n"/>
       <c r="P20" s="6" t="n"/>
       <c r="Q20" s="6" t="n"/>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R20" s="6" t="n"/>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
       <c r="U20" s="6" t="n"/>
@@ -2268,41 +1884,13 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
@@ -2312,11 +1900,7 @@
       <c r="O21" s="6" t="n"/>
       <c r="P21" s="6" t="n"/>
       <c r="Q21" s="6" t="n"/>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R21" s="6" t="n"/>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
       <c r="U21" s="6" t="n"/>
@@ -2332,41 +1916,13 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="n"/>
@@ -2376,11 +1932,7 @@
       <c r="O22" s="6" t="n"/>
       <c r="P22" s="6" t="n"/>
       <c r="Q22" s="6" t="n"/>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R22" s="6" t="n"/>
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="6" t="n"/>
       <c r="U22" s="6" t="n"/>
@@ -2396,41 +1948,13 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -2440,11 +1964,7 @@
       <c r="O23" s="6" t="n"/>
       <c r="P23" s="6" t="n"/>
       <c r="Q23" s="6" t="n"/>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R23" s="6" t="n"/>
       <c r="S23" s="6" t="n"/>
       <c r="T23" s="6" t="n"/>
       <c r="U23" s="6" t="n"/>
@@ -2460,41 +1980,13 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
       <c r="I24" s="6" t="n"/>
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="n"/>
@@ -2504,11 +1996,7 @@
       <c r="O24" s="6" t="n"/>
       <c r="P24" s="6" t="n"/>
       <c r="Q24" s="6" t="n"/>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R24" s="6" t="n"/>
       <c r="S24" s="6" t="n"/>
       <c r="T24" s="6" t="n"/>
       <c r="U24" s="6" t="n"/>
@@ -2524,41 +2012,13 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="n"/>
@@ -2568,11 +2028,7 @@
       <c r="O25" s="6" t="n"/>
       <c r="P25" s="6" t="n"/>
       <c r="Q25" s="6" t="n"/>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R25" s="6" t="n"/>
       <c r="S25" s="6" t="n"/>
       <c r="T25" s="6" t="n"/>
       <c r="U25" s="6" t="n"/>
@@ -2588,41 +2044,13 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="n"/>
@@ -2632,11 +2060,7 @@
       <c r="O26" s="6" t="n"/>
       <c r="P26" s="6" t="n"/>
       <c r="Q26" s="6" t="n"/>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R26" s="6" t="n"/>
       <c r="S26" s="6" t="n"/>
       <c r="T26" s="6" t="n"/>
       <c r="U26" s="6" t="n"/>
@@ -2652,41 +2076,13 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n"/>
@@ -2696,11 +2092,7 @@
       <c r="O27" s="6" t="n"/>
       <c r="P27" s="6" t="n"/>
       <c r="Q27" s="6" t="n"/>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R27" s="6" t="n"/>
       <c r="S27" s="6" t="n"/>
       <c r="T27" s="6" t="n"/>
       <c r="U27" s="6" t="n"/>
@@ -2716,41 +2108,13 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="6" t="n"/>
@@ -2760,11 +2124,7 @@
       <c r="O28" s="6" t="n"/>
       <c r="P28" s="6" t="n"/>
       <c r="Q28" s="6" t="n"/>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R28" s="6" t="n"/>
       <c r="S28" s="6" t="n"/>
       <c r="T28" s="6" t="n"/>
       <c r="U28" s="6" t="n"/>
@@ -2780,41 +2140,13 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="6" t="n"/>
@@ -2824,11 +2156,7 @@
       <c r="O29" s="6" t="n"/>
       <c r="P29" s="6" t="n"/>
       <c r="Q29" s="6" t="n"/>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R29" s="6" t="n"/>
       <c r="S29" s="6" t="n"/>
       <c r="T29" s="6" t="n"/>
       <c r="U29" s="6" t="n"/>
@@ -2844,41 +2172,13 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="6" t="n"/>
@@ -2888,11 +2188,7 @@
       <c r="O30" s="6" t="n"/>
       <c r="P30" s="6" t="n"/>
       <c r="Q30" s="6" t="n"/>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R30" s="6" t="n"/>
       <c r="S30" s="6" t="n"/>
       <c r="T30" s="6" t="n"/>
       <c r="U30" s="6" t="n"/>
@@ -2908,41 +2204,13 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="6" t="n"/>
@@ -2952,11 +2220,7 @@
       <c r="O31" s="6" t="n"/>
       <c r="P31" s="6" t="n"/>
       <c r="Q31" s="6" t="n"/>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R31" s="6" t="n"/>
       <c r="S31" s="6" t="n"/>
       <c r="T31" s="6" t="n"/>
       <c r="U31" s="6" t="n"/>
@@ -2972,41 +2236,13 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="n"/>
@@ -3016,11 +2252,7 @@
       <c r="O32" s="6" t="n"/>
       <c r="P32" s="6" t="n"/>
       <c r="Q32" s="6" t="n"/>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="R32" s="6" t="n"/>
       <c r="S32" s="6" t="n"/>
       <c r="T32" s="6" t="n"/>
       <c r="U32" s="6" t="n"/>
@@ -3034,426 +2266,6 @@
       <c r="AC32" s="6" t="n"/>
       <c r="AD32" s="6" t="n"/>
     </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1833025</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>S00022</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="R3:AD3"/>
